--- a/My project/JsonConverter/ExcelFiles/Customer.xlsx
+++ b/My project/JsonConverter/ExcelFiles/Customer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MonsterRestaurant\My project\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B7E8D6-A48B-45B2-8ABA-97A2A477887B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB253A17-65BB-4227-9C46-24BE80209F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
   <si>
     <t>(name)</t>
   </si>
@@ -82,37 +82,6 @@
     <t>Dokkaebi_Order_10</t>
   </si>
   <si>
-    <t>도깨비의 주문1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>도깨비의 주문2</t>
-  </si>
-  <si>
-    <t>도깨비의 주문3</t>
-  </si>
-  <si>
-    <t>도깨비의 주문4</t>
-  </si>
-  <si>
-    <t>도깨비의 주문5</t>
-  </si>
-  <si>
-    <t>도깨비의 주문6</t>
-  </si>
-  <si>
-    <t>도깨비의 주문7</t>
-  </si>
-  <si>
-    <t>도깨비의 주문8</t>
-  </si>
-  <si>
-    <t>도깨비의 주문9</t>
-  </si>
-  <si>
-    <t>도깨비의 주문10</t>
-  </si>
-  <si>
     <t>오늘은 바삭한 식감이 좋겠어.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -162,6 +131,10 @@
   </si>
   <si>
     <t>Potato_Food_02</t>
+  </si>
+  <si>
+    <t>도깨비의 주문</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -627,7 +600,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E3" s="25"/>
     </row>
@@ -636,13 +609,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="3"/>
@@ -661,13 +634,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="3"/>
@@ -686,13 +659,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="3"/>
@@ -711,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>30</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="3"/>
@@ -736,13 +709,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="3"/>
@@ -761,13 +734,13 @@
         <v>12</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>32</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="3"/>
@@ -786,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>33</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="3"/>
@@ -811,13 +784,13 @@
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>34</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="3"/>
@@ -836,13 +809,13 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>35</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="3"/>
@@ -861,13 +834,13 @@
         <v>16</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>36</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="3"/>
